--- a/events/Szeged_2013_WC/Szeged_2013_WC_Results.xlsx
+++ b/events/Szeged_2013_WC/Szeged_2013_WC_Results.xlsx
@@ -1272,6 +1272,11 @@
           <t>0:00:00.414</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1867,6 +1872,11 @@
           <t>0:00:00.942</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>42573</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2682,6 +2692,11 @@
           <t>0:00:04.506</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2812,6 +2827,11 @@
           <t>0:01:48.280</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3432,6 +3452,11 @@
           <t>0:00:03.936</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3642,6 +3667,11 @@
           <t>0:00:14.610</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>104031</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4412,6 +4442,11 @@
           <t>0:00:03.546</t>
         </is>
       </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4677,6 +4712,11 @@
           <t>0:03:47.548</t>
         </is>
       </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5147,6 +5187,11 @@
           <t>0:00:36.852</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6162,6 +6207,11 @@
           <t>0:03:57.636</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6707,6 +6757,11 @@
           <t>0:00:01.368</t>
         </is>
       </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7522,6 +7577,11 @@
           <t>0:00:21.456</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8357,6 +8417,11 @@
           <t>36450</t>
         </is>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8497,6 +8562,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8632,6 +8702,11 @@
           <t>0:00:40.890</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>71239</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8907,6 +8982,11 @@
           <t>0:00:02.190</t>
         </is>
       </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>42049</t>
@@ -9197,6 +9277,11 @@
           <t>0:00:09.762</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>42131</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10322,6 +10407,11 @@
           <t>0:00:22.476</t>
         </is>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10932,6 +11022,11 @@
           <t>0:00:13.326</t>
         </is>
       </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>45224</t>
@@ -11661,6 +11756,11 @@
           <t>0:00:07.416</t>
         </is>
       </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>42573</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -13391,6 +13491,16 @@
           <t>0:00:02.274</t>
         </is>
       </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
       <c r="U188" t="inlineStr">
         <is>
           <t>36153</t>
@@ -13466,6 +13576,11 @@
           <t>36742</t>
         </is>
       </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>36743</t>
+        </is>
+      </c>
       <c r="T189" t="inlineStr">
         <is>
           <t>35992</t>
@@ -13976,6 +14091,11 @@
           <t>0:00:02.490</t>
         </is>
       </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -14656,6 +14776,11 @@
           <t>0:00:04.620</t>
         </is>
       </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>42573</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -15581,6 +15706,11 @@
           <t>0:00:13.050</t>
         </is>
       </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -15776,6 +15906,11 @@
           <t>0:00:01.368</t>
         </is>
       </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -16706,6 +16841,11 @@
           <t>0:00:12.966</t>
         </is>
       </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>104031</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -16766,6 +16906,11 @@
           <t>0:03:50.373</t>
         </is>
       </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -16831,6 +16976,11 @@
           <t>0:00:00.960</t>
         </is>
       </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -17106,6 +17256,11 @@
           <t>0:00:08.082</t>
         </is>
       </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -19206,6 +19361,11 @@
           <t>0:04:20.537</t>
         </is>
       </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -19681,6 +19841,11 @@
           <t>0:00:23.226</t>
         </is>
       </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -20641,6 +20806,11 @@
           <t>36450</t>
         </is>
       </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -20926,6 +21096,11 @@
           <t>0:00:08.622</t>
         </is>
       </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
       <c r="S298" t="inlineStr">
         <is>
           <t>42049</t>
@@ -21631,6 +21806,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -21691,6 +21871,11 @@
           <t>0:03:58.862</t>
         </is>
       </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
       <c r="S309" t="inlineStr">
         <is>
           <t>45224</t>
@@ -22046,6 +22231,11 @@
           <t>0:00:13.602</t>
         </is>
       </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -23331,6 +23521,11 @@
           <t>0:00:16.572</t>
         </is>
       </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>42573</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -23691,6 +23886,11 @@
           <t>36742</t>
         </is>
       </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>36743</t>
+        </is>
+      </c>
       <c r="T338" t="inlineStr">
         <is>
           <t>35992</t>
@@ -24976,6 +25176,11 @@
           <t>0:00:02.490</t>
         </is>
       </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -25436,6 +25641,11 @@
           <t>0:00:06.342</t>
         </is>
       </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -25631,6 +25841,11 @@
           <t>0:00:12.696</t>
         </is>
       </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -25756,6 +25971,11 @@
           <t>0:01:51.925</t>
         </is>
       </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -26436,6 +26656,11 @@
           <t>0:00:03.402</t>
         </is>
       </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>42725</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -26571,6 +26796,11 @@
           <t>0:00:09.228</t>
         </is>
       </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>99871</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -26701,6 +26931,11 @@
           <t>0:02:00.045</t>
         </is>
       </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -26836,6 +27071,11 @@
           <t>0:00:14.088</t>
         </is>
       </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>169726</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -27301,6 +27541,11 @@
           <t>0:00:04.962</t>
         </is>
       </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -28126,6 +28371,11 @@
           <t>0:00:01.236</t>
         </is>
       </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
       <c r="S403" t="inlineStr">
         <is>
           <t>42049</t>
@@ -29885,6 +30135,11 @@
           <t>36450</t>
         </is>
       </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -30250,6 +30505,11 @@
           <t>36742</t>
         </is>
       </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>36743</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -30320,6 +30580,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -30945,6 +31210,11 @@
           <t>42151</t>
         </is>
       </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -31949,6 +32219,11 @@
           <t>0:00:00.732</t>
         </is>
       </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -32289,6 +32564,11 @@
           <t>0:00:06.348</t>
         </is>
       </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -32408,6 +32688,11 @@
       <c r="L465" t="n">
         <v>9</v>
       </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
       <c r="X465" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -33093,6 +33378,11 @@
           <t>0:01:44.670</t>
         </is>
       </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -33433,6 +33723,11 @@
           <t>0:00:09.024</t>
         </is>
       </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>99871</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -33563,6 +33858,11 @@
           <t>0:00:16.386</t>
         </is>
       </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>42725</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -33623,6 +33923,11 @@
           <t>0:01:58.863</t>
         </is>
       </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -34028,6 +34333,11 @@
           <t>0:00:11.988</t>
         </is>
       </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>169726</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -35868,6 +36178,11 @@
           <t>0:00:03.636</t>
         </is>
       </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
       <c r="S515" t="inlineStr">
         <is>
           <t>42049</t>
@@ -35943,6 +36258,11 @@
           <t>36742</t>
         </is>
       </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>36743</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -36508,6 +36828,11 @@
           <t>36450</t>
         </is>
       </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -36578,6 +36903,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -37189,6 +37519,11 @@
           <t>0:00:01.068</t>
         </is>
       </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>42573</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -38197,6 +38532,11 @@
           <t>0:00:08.982</t>
         </is>
       </c>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>104031</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -38470,6 +38810,11 @@
           <t>0:00:02.214</t>
         </is>
       </c>
+      <c r="R552" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -40640,6 +40985,11 @@
           <t>36450</t>
         </is>
       </c>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -41052,6 +41402,11 @@
           <t>0:00:06.870</t>
         </is>
       </c>
+      <c r="R589" t="inlineStr">
+        <is>
+          <t>42573</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -41963,6 +42318,11 @@
           <t>0:00:03.534</t>
         </is>
       </c>
+      <c r="R602" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -42169,6 +42529,11 @@
           <t>0:00:00.264</t>
         </is>
       </c>
+      <c r="S605" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -42591,6 +42956,11 @@
           <t>0:00:05.748</t>
         </is>
       </c>
+      <c r="S611" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -42802,6 +43172,11 @@
           <t>0:00:02.172</t>
         </is>
       </c>
+      <c r="R614" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -43085,6 +43460,11 @@
           <t>0:00:07.644</t>
         </is>
       </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -43795,6 +44175,11 @@
           <t>0:00:12.240</t>
         </is>
       </c>
+      <c r="R628" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -45168,6 +45553,11 @@
           <t>0:00:12.150</t>
         </is>
       </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
       <c r="S647" t="inlineStr">
         <is>
           <t>45224</t>
@@ -46284,6 +46674,11 @@
           <t>0:00:08.502</t>
         </is>
       </c>
+      <c r="S663" t="inlineStr">
+        <is>
+          <t>104031</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -46991,6 +47386,16 @@
           <t>0:00:06.732</t>
         </is>
       </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
       <c r="U672" t="inlineStr">
         <is>
           <t>36153</t>
@@ -47150,6 +47555,11 @@
           <t>36742</t>
         </is>
       </c>
+      <c r="S674" t="inlineStr">
+        <is>
+          <t>36743</t>
+        </is>
+      </c>
       <c r="T674" t="inlineStr">
         <is>
           <t>35992</t>
@@ -47232,6 +47642,11 @@
           <t>36162</t>
         </is>
       </c>
+      <c r="U675" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -47304,6 +47719,11 @@
           <t>47426</t>
         </is>
       </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
       <c r="T676" t="inlineStr">
         <is>
           <t>47436</t>
@@ -47836,6 +48256,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T683" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -47986,6 +48411,11 @@
           <t>36165</t>
         </is>
       </c>
+      <c r="T685" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -49086,6 +49516,11 @@
           <t>0:00:01.950</t>
         </is>
       </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -50221,6 +50656,11 @@
           <t>0:00:05.178</t>
         </is>
       </c>
+      <c r="R718" t="inlineStr">
+        <is>
+          <t>99871</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -50686,6 +51126,11 @@
           <t>0:00:09.030</t>
         </is>
       </c>
+      <c r="R725" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -50746,6 +51191,11 @@
           <t>0:00:41.060</t>
         </is>
       </c>
+      <c r="R726" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -51891,6 +52341,11 @@
           <t>0:00:40.595</t>
         </is>
       </c>
+      <c r="R743" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -52096,6 +52551,11 @@
           <t>0:00:02.922</t>
         </is>
       </c>
+      <c r="R746" t="inlineStr">
+        <is>
+          <t>169726</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -53025,6 +53485,11 @@
           <t>0:00:43.292</t>
         </is>
       </c>
+      <c r="R760" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -53295,6 +53760,11 @@
           <t>0:00:01.494</t>
         </is>
       </c>
+      <c r="R764" t="inlineStr">
+        <is>
+          <t>42573</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -53749,6 +54219,11 @@
           <t>0:00:00.306</t>
         </is>
       </c>
+      <c r="R771" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -54674,6 +55149,11 @@
           <t>0:00:33.240</t>
         </is>
       </c>
+      <c r="R785" t="inlineStr">
+        <is>
+          <t>42725</t>
+        </is>
+      </c>
       <c r="S785" t="inlineStr">
         <is>
           <t>42726</t>
@@ -57063,6 +57543,11 @@
           <t>0:00:01.632</t>
         </is>
       </c>
+      <c r="S819" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -57818,6 +58303,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="S830" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -58958,6 +59448,11 @@
           <t>0:00:07.128</t>
         </is>
       </c>
+      <c r="R846" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -59482,6 +59977,11 @@
           <t>0:00:03.834</t>
         </is>
       </c>
+      <c r="R854" t="inlineStr">
+        <is>
+          <t>99871</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -59882,6 +60382,11 @@
           <t>0:00:01.338</t>
         </is>
       </c>
+      <c r="R860" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -61147,6 +61652,11 @@
           <t>0:00:01.470</t>
         </is>
       </c>
+      <c r="R879" t="inlineStr">
+        <is>
+          <t>169726</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -62141,6 +62651,11 @@
           <t>0:00:00.600</t>
         </is>
       </c>
+      <c r="R894" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -62276,6 +62791,11 @@
           <t>0:00:01.104</t>
         </is>
       </c>
+      <c r="R896" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
@@ -63686,6 +64206,11 @@
           <t>0:00:02.916</t>
         </is>
       </c>
+      <c r="R917" t="inlineStr">
+        <is>
+          <t>42573</t>
+        </is>
+      </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
@@ -65166,6 +65691,11 @@
           <t>0:00:38.950</t>
         </is>
       </c>
+      <c r="S938" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
@@ -66254,6 +66784,11 @@
           <t>0:00:01.932</t>
         </is>
       </c>
+      <c r="R954" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
@@ -66532,6 +67067,11 @@
           <t>0:00:08.802</t>
         </is>
       </c>
+      <c r="R958" t="inlineStr">
+        <is>
+          <t>99871</t>
+        </is>
+      </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
@@ -67839,6 +68379,11 @@
           <t>0:00:18.516</t>
         </is>
       </c>
+      <c r="R977" t="inlineStr">
+        <is>
+          <t>169726</t>
+        </is>
+      </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
@@ -68869,6 +69414,11 @@
           <t>0:00:01.470</t>
         </is>
       </c>
+      <c r="R992" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
@@ -69358,6 +69908,11 @@
           <t>0:00:00.630</t>
         </is>
       </c>
+      <c r="R999" t="inlineStr">
+        <is>
+          <t>169726</t>
+        </is>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
@@ -69765,6 +70320,11 @@
           <t>0:00:42.565</t>
         </is>
       </c>
+      <c r="R1005" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
@@ -71205,6 +71765,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T1025" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
@@ -71441,6 +72006,11 @@
           <t>36165</t>
         </is>
       </c>
+      <c r="T1028" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
@@ -71749,6 +72319,11 @@
           <t>0:01:39.148</t>
         </is>
       </c>
+      <c r="R1032" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
@@ -72320,6 +72895,11 @@
           <t>0:00:14.946</t>
         </is>
       </c>
+      <c r="R1040" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
@@ -72454,6 +73034,11 @@
           <t>0:00:00.234</t>
         </is>
       </c>
+      <c r="R1042" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
@@ -72665,6 +73250,11 @@
           <t>0:00:01.938</t>
         </is>
       </c>
+      <c r="R1045" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
@@ -73648,6 +74238,11 @@
           <t>0:00:39.872</t>
         </is>
       </c>
+      <c r="R1059" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
@@ -73998,6 +74593,11 @@
           <t>0:00:03.180</t>
         </is>
       </c>
+      <c r="R1064" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
@@ -74415,6 +75015,11 @@
           <t>0:00:01.056</t>
         </is>
       </c>
+      <c r="R1070" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
@@ -75418,6 +76023,11 @@
           <t>0:00:01.158</t>
         </is>
       </c>
+      <c r="R1084" t="inlineStr">
+        <is>
+          <t>42725</t>
+        </is>
+      </c>
       <c r="S1084" t="inlineStr">
         <is>
           <t>42726</t>
@@ -76071,6 +76681,11 @@
           <t>0:00:02.394</t>
         </is>
       </c>
+      <c r="S1093" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
@@ -76498,6 +77113,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="S1099" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
@@ -78693,6 +79313,11 @@
           <t>42151</t>
         </is>
       </c>
+      <c r="S1129" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
@@ -79500,6 +80125,11 @@
           <t>0:00:06.534</t>
         </is>
       </c>
+      <c r="R1140" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
       <c r="S1140" t="inlineStr">
         <is>
           <t>42258</t>
@@ -79782,6 +80412,11 @@
           <t>0:00:44.700</t>
         </is>
       </c>
+      <c r="R1144" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
@@ -81422,6 +82057,11 @@
           <t>0:20:15.767</t>
         </is>
       </c>
+      <c r="R1168" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
@@ -82197,6 +82837,11 @@
       <c r="Q1179" t="inlineStr">
         <is>
           <t>0:01:19.542</t>
+        </is>
+      </c>
+      <c r="R1179" t="inlineStr">
+        <is>
+          <t>36743</t>
         </is>
       </c>
     </row>
@@ -83018,7 +83663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D251"/>
+  <dimension ref="A1:D282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88543,6 +89188,688 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>SHTYL</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Ilia</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>SHTOKALOV</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>PODOLSKAIA</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>ANIUSHINA</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>WALKER</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>BOYTON</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>RIBEIRO</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Miika</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>NYKAENEN</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>36743</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Eivind</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>VOLD</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>KHUDZENKA</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Aliksandr</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>LIAPIOSHKA</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>42131</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Aleksandr</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>SERGEEV</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Maxim</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>SPESIVTSEV</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Svetlana</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>CHERNIGOVSKAYA</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>WALLACE</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>HORNSBY</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Helder</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>42573</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Natalya</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>SERGEYEVA</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>42725</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>CORREA</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Tamas</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>KISS</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>71239</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Kaibo</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Mia</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>FRIEND CHUNG</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>99871</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Marko</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>LIPOVAC</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Wei Liang Bill</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>LEE</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>104031</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Xiaoyun</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>ZENG</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Gabor</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SZABO</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>169726</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Kaito</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>NAGAI</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Oleg</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>SHELEGOV</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
